--- a/data/trans_dic/P41E_2023_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes</t>
+          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 16,8</t>
+          <t>1,81; 17,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 19,54</t>
+          <t>2,89; 19,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 14,86</t>
+          <t>3,65; 14,72</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,98</t>
+          <t>0,63; 6,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,19</t>
+          <t>0,59; 5,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,04</t>
+          <t>0,91; 4,03</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,18</t>
+          <t>1,15; 4,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,14</t>
+          <t>1,14; 4,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,58</t>
+          <t>1,46; 3,79</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,15</t>
+          <t>0,78; 6,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,9</t>
+          <t>4,7; 8,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,42</t>
+          <t>1,94; 6,52</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,86; 19,11</t>
+          <t>12,02; 19,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,32; 21,0</t>
+          <t>14,34; 20,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,94; 19,01</t>
+          <t>14,1; 18,91</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,56; 31,07</t>
+          <t>20,97; 30,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 31,52</t>
+          <t>3,23; 31,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,77; 28,51</t>
+          <t>6,74; 28,46</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,03; 44,7</t>
+          <t>30,83; 44,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,41; 49,83</t>
+          <t>37,21; 50,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,45; 45,16</t>
+          <t>36,1; 45,58</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,83; 11,89</t>
+          <t>6,33; 12,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,97</t>
+          <t>6,91; 13,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,08</t>
+          <t>7,58; 12,09</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes</t>
+          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1804; 16704</t>
+          <t>1798; 17241</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2734; 15579</t>
+          <t>2305; 15943</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6853; 26637</t>
+          <t>6542; 26370</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1217; 11478</t>
+          <t>1211; 12753</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1092; 10415</t>
+          <t>1177; 10323</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3335; 15870</t>
+          <t>3580; 15808</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3093; 12121</t>
+          <t>3334; 13195</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3070; 11583</t>
+          <t>3179; 12200</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7948; 20413</t>
+          <t>8342; 21565</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3826; 34000</t>
+          <t>4334; 33907</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16494; 32004</t>
+          <t>16916; 31246</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17690; 58576</t>
+          <t>17695; 59479</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37489; 60416</t>
+          <t>37993; 60780</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40537; 59462</t>
+          <t>40594; 58659</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83510; 113899</t>
+          <t>84468; 113283</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40635; 61396</t>
+          <t>41444; 60587</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12696; 111956</t>
+          <t>11467; 113107</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37427; 157582</t>
+          <t>37277; 157324</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34227; 49312</t>
+          <t>34008; 49589</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40954; 54551</t>
+          <t>40738; 55233</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77922; 99250</t>
+          <t>79336; 100176</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>102485; 209182</t>
+          <t>111245; 214306</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>120512; 216301</t>
+          <t>115136; 216997</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>271699; 413790</t>
+          <t>259713; 414366</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41E_2023_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 17,34</t>
+          <t>1,67; 15,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 19,99</t>
+          <t>2,79; 19,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 14,72</t>
+          <t>3,32; 12,99</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,64</t>
+          <t>0,58; 5,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,15</t>
+          <t>0,42; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,03</t>
+          <t>0,8; 3,82</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,55</t>
+          <t>1,15; 4,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,36</t>
+          <t>1,0; 3,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,79</t>
+          <t>1,4; 3,54</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,13</t>
+          <t>3,28; 7,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,69</t>
+          <t>4,57; 8,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,52</t>
+          <t>4,48; 7,46</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 19,23</t>
+          <t>11,95; 19,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,34; 20,72</t>
+          <t>14,37; 21,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,1; 18,91</t>
+          <t>14,17; 18,77</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,97; 30,66</t>
+          <t>20,62; 30,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 31,85</t>
+          <t>25,63; 36,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,74; 28,46</t>
+          <t>23,76; 30,83</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,83; 44,95</t>
+          <t>31,36; 44,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,21; 50,45</t>
+          <t>37,47; 50,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,1; 45,58</t>
+          <t>35,98; 45,75</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,19</t>
+          <t>9,85; 12,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,91; 13,01</t>
+          <t>11,11; 13,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,09</t>
+          <t>10,88; 12,76</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>13704</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1798; 17241</t>
+          <t>1631; 14710</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2305; 15943</t>
+          <t>2438; 16978</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6542; 26370</t>
+          <t>6150; 24051</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8148</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1211; 12753</t>
+          <t>1255; 10875</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1177; 10323</t>
+          <t>949; 8933</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3580; 15808</t>
+          <t>3524; 16905</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>14574</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3334; 13195</t>
+          <t>3849; 14817</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3179; 12200</t>
+          <t>3191; 12655</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8342; 21565</t>
+          <t>9150; 23123</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23111</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>41477</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4334; 33907</t>
+          <t>10915; 25786</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16916; 31246</t>
+          <t>17653; 33061</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17695; 59479</t>
+          <t>32202; 53642</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>48299</t>
+          <t>51412</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49319</t>
+          <t>55890</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97618</t>
+          <t>107302</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37993; 60780</t>
+          <t>40786; 64927</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40594; 58659</t>
+          <t>45531; 66845</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84468; 113283</t>
+          <t>93270; 123511</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>50139</t>
+          <t>54876</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>45374</t>
+          <t>50325</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95513</t>
+          <t>105201</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41444; 60587</t>
+          <t>44729; 65555</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11467; 113107</t>
+          <t>42198; 59782</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37277; 157324</t>
+          <t>90664; 117659</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>41489</t>
+          <t>44818</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>47505</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88994</t>
+          <t>96658</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34008; 49589</t>
+          <t>37396; 53576</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40738; 55233</t>
+          <t>44229; 59608</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79336; 100176</t>
+          <t>85369; 108556</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>174371</t>
+          <t>186425</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>183107</t>
+          <t>200639</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>357478</t>
+          <t>387064</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>111245; 214306</t>
+          <t>163464; 210543</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>115136; 216997</t>
+          <t>179746; 222327</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>259713; 414366</t>
+          <t>356631; 418249</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41E_2023_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
+          <t>Población que con respecto al último año sus relaciones sexuales no han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
+          <t>Población que con respecto al último año sus relaciones sexuales no han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
